--- a/input/data/original/Data_centers_Chile_13102026.xlsx
+++ b/input/data/original/Data_centers_Chile_13102026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\M-New\Paola Tubaro\datacenters-chile\input\data\original\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A6B000-7E53-43C5-AF25-5E7258D5CA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D686649-06F7-4BA3-91A1-F3130D254401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4366,7 +4366,7 @@
         <v>418</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="H89">
         <v>75</v>
